--- a/outputs/uploaded_file_ids.xlsx
+++ b/outputs/uploaded_file_ids.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>filename</t>
   </si>
@@ -25,25 +25,13 @@
     <t>AIPPI position paper on the CPVO.CPVR Call for Evidence March 2025.pdf</t>
   </si>
   <si>
-    <t>APBREBES (2020) Focus on Plant Variety Protection UPOV Literature Review.pdf</t>
-  </si>
-  <si>
     <t>Adelaiye, V.O. (2024) Plant Variety Right and Intellectual Property Law in Nigeria A Review.pdf</t>
   </si>
   <si>
-    <t>Glastuinbouw position paper on the CPVO.CPVR Call for Evidence March 2025.pdf</t>
-  </si>
-  <si>
     <t>C:\Users\Vincent.Frippiat\OneDrive - Ecorys\Documents\PnR\Sustainable Agriculture\PDF Processing Eleonora\lit_review\pdfs\AIPPI position paper on the CPVO.CPVR Call for Evidence March 2025.pdf</t>
   </si>
   <si>
-    <t>C:\Users\Vincent.Frippiat\OneDrive - Ecorys\Documents\PnR\Sustainable Agriculture\PDF Processing Eleonora\lit_review\pdfs\APBREBES (2020) Focus on Plant Variety Protection UPOV Literature Review.pdf</t>
-  </si>
-  <si>
     <t>C:\Users\Vincent.Frippiat\OneDrive - Ecorys\Documents\PnR\Sustainable Agriculture\PDF Processing Eleonora\lit_review\pdfs\Adelaiye, V.O. (2024) Plant Variety Right and Intellectual Property Law in Nigeria A Review.pdf</t>
-  </si>
-  <si>
-    <t>C:\Users\Vincent.Frippiat\OneDrive - Ecorys\Documents\PnR\Sustainable Agriculture\PDF Processing Eleonora\lit_review\pdfs\Glastuinbouw position paper on the CPVO.CPVR Call for Evidence March 2025.pdf</t>
   </si>
 </sst>
 </file>
@@ -401,7 +389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -417,7 +405,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -425,23 +413,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
         <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/uploaded_file_ids.xlsx
+++ b/outputs/uploaded_file_ids.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>filename</t>
   </si>
@@ -22,13 +22,7 @@
     <t>file_id</t>
   </si>
   <si>
-    <t>AIPPI position paper on the CPVO.CPVR Call for Evidence March 2025.pdf</t>
-  </si>
-  <si>
     <t>Adelaiye, V.O. (2024) Plant Variety Right and Intellectual Property Law in Nigeria A Review.pdf</t>
-  </si>
-  <si>
-    <t>C:\Users\Vincent.Frippiat\OneDrive - Ecorys\Documents\PnR\Sustainable Agriculture\PDF Processing Eleonora\lit_review\pdfs\AIPPI position paper on the CPVO.CPVR Call for Evidence March 2025.pdf</t>
   </si>
   <si>
     <t>C:\Users\Vincent.Frippiat\OneDrive - Ecorys\Documents\PnR\Sustainable Agriculture\PDF Processing Eleonora\lit_review\pdfs\Adelaiye, V.O. (2024) Plant Variety Right and Intellectual Property Law in Nigeria A Review.pdf</t>
@@ -389,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -405,15 +399,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
         <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
